--- a/output/qa/split_data_v2.xlsx
+++ b/output/qa/split_data_v2.xlsx
@@ -607,7 +607,7 @@
         <v>3383</v>
       </c>
       <c r="O2" t="n">
-        <v>96.51000000000001</v>
+        <v>99.88</v>
       </c>
       <c r="P2" t="n">
         <v>96.51000000000001</v>
@@ -906,7 +906,7 @@
         <v>1621</v>
       </c>
       <c r="O3" t="n">
-        <v>96.42</v>
+        <v>99.94</v>
       </c>
       <c r="P3" t="n">
         <v>96.42</v>
@@ -985,7 +985,7 @@
         <v>943</v>
       </c>
       <c r="O4" t="n">
-        <v>95.23</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
         <v>95.23</v>
@@ -1222,7 +1222,7 @@
         <v>495</v>
       </c>
       <c r="O7" t="n">
-        <v>97.78</v>
+        <v>99.39</v>
       </c>
       <c r="P7" t="n">
         <v>97.78</v>
@@ -1380,7 +1380,7 @@
         <v>264</v>
       </c>
       <c r="O9" t="n">
-        <v>98.48</v>
+        <v>100</v>
       </c>
       <c r="P9" t="n">
         <v>98.48</v>
@@ -1758,10 +1758,10 @@
         <v>114</v>
       </c>
       <c r="O3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P3" t="n">
         <v>95.614035</v>
-      </c>
-      <c r="P3" t="n">
-        <v>100</v>
       </c>
       <c r="Q3" t="n">
         <v>10</v>
@@ -2074,10 +2074,10 @@
         <v>19</v>
       </c>
       <c r="O7" t="n">
+        <v>100</v>
+      </c>
+      <c r="P7" t="n">
         <v>89.47368400000001</v>
-      </c>
-      <c r="P7" t="n">
-        <v>100</v>
       </c>
       <c r="Q7" t="n">
         <v>43</v>
@@ -2232,10 +2232,10 @@
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -2311,10 +2311,10 @@
         <v>68</v>
       </c>
       <c r="O10" t="n">
+        <v>100</v>
+      </c>
+      <c r="P10" t="n">
         <v>97.058824</v>
-      </c>
-      <c r="P10" t="n">
-        <v>100</v>
       </c>
       <c r="Q10" t="n">
         <v>19</v>
@@ -2548,10 +2548,10 @@
         <v>1621</v>
       </c>
       <c r="O13" t="n">
+        <v>99.93831</v>
+      </c>
+      <c r="P13" t="n">
         <v>96.42196199999999</v>
-      </c>
-      <c r="P13" t="n">
-        <v>99.93831</v>
       </c>
       <c r="Q13" t="n">
         <v>51</v>
@@ -3591,10 +3591,10 @@
         <v>943</v>
       </c>
       <c r="O26" t="n">
+        <v>100</v>
+      </c>
+      <c r="P26" t="n">
         <v>95.227996</v>
-      </c>
-      <c r="P26" t="n">
-        <v>100</v>
       </c>
       <c r="Q26" t="n">
         <v>113</v>
@@ -3670,10 +3670,10 @@
         <v>16</v>
       </c>
       <c r="O27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P27" t="n">
         <v>93.75</v>
-      </c>
-      <c r="P27" t="n">
-        <v>100</v>
       </c>
       <c r="Q27" t="n">
         <v>11</v>
@@ -4480,7 +4480,7 @@
         <v>3622</v>
       </c>
       <c r="P2" t="n">
-        <v>96.94</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="Q2" t="n">
         <v>96.94</v>
@@ -4561,7 +4561,7 @@
         <v>3383</v>
       </c>
       <c r="P3" t="n">
-        <v>96.51000000000001</v>
+        <v>99.88</v>
       </c>
       <c r="Q3" t="n">
         <v>96.51000000000001</v>
@@ -4864,7 +4864,7 @@
         <v>1669</v>
       </c>
       <c r="P3" t="n">
-        <v>97.18000000000001</v>
+        <v>99.88</v>
       </c>
       <c r="Q3" t="n">
         <v>97.18000000000001</v>
@@ -4945,7 +4945,7 @@
         <v>944</v>
       </c>
       <c r="P4" t="n">
-        <v>95.66</v>
+        <v>94.39</v>
       </c>
       <c r="Q4" t="n">
         <v>95.66</v>
@@ -5188,7 +5188,7 @@
         <v>465</v>
       </c>
       <c r="P7" t="n">
-        <v>98.06</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>98.06</v>
@@ -5269,7 +5269,7 @@
         <v>105</v>
       </c>
       <c r="P8" t="n">
-        <v>91.43000000000001</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="Q8" t="n">
         <v>91.43000000000001</v>
@@ -5350,7 +5350,7 @@
         <v>436</v>
       </c>
       <c r="P9" t="n">
-        <v>98.84999999999999</v>
+        <v>98.62</v>
       </c>
       <c r="Q9" t="n">
         <v>98.84999999999999</v>
@@ -5593,7 +5593,7 @@
         <v>1621</v>
       </c>
       <c r="P12" t="n">
-        <v>96.42</v>
+        <v>99.94</v>
       </c>
       <c r="Q12" t="n">
         <v>96.42</v>
@@ -5674,7 +5674,7 @@
         <v>943</v>
       </c>
       <c r="P13" t="n">
-        <v>95.23</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
         <v>95.23</v>
@@ -5917,7 +5917,7 @@
         <v>495</v>
       </c>
       <c r="P16" t="n">
-        <v>97.78</v>
+        <v>99.39</v>
       </c>
       <c r="Q16" t="n">
         <v>97.78</v>
@@ -6079,7 +6079,7 @@
         <v>264</v>
       </c>
       <c r="P18" t="n">
-        <v>98.48</v>
+        <v>100</v>
       </c>
       <c r="Q18" t="n">
         <v>98.48</v>
@@ -6471,10 +6471,10 @@
         <v>114</v>
       </c>
       <c r="P3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" t="n">
         <v>99.12280699999999</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>100</v>
       </c>
       <c r="R3" t="n">
         <v>11</v>
@@ -6639,10 +6639,10 @@
         <v>187</v>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>96.791444</v>
       </c>
       <c r="Q5" t="n">
-        <v>96.791444</v>
+        <v>100</v>
       </c>
       <c r="R5" t="n">
         <v>46</v>
@@ -6807,10 +6807,10 @@
         <v>19</v>
       </c>
       <c r="P7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q7" t="n">
         <v>84.210526</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>100</v>
       </c>
       <c r="R7" t="n">
         <v>17</v>
@@ -6975,10 +6975,10 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>4</v>
@@ -7059,10 +7059,10 @@
         <v>42</v>
       </c>
       <c r="P10" t="n">
+        <v>97.61904800000001</v>
+      </c>
+      <c r="Q10" t="n">
         <v>92.85714299999999</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>97.61904800000001</v>
       </c>
       <c r="R10" t="n">
         <v>24</v>
@@ -7143,10 +7143,10 @@
         <v>115</v>
       </c>
       <c r="P11" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q11" t="n">
         <v>97.39130400000001</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>100</v>
       </c>
       <c r="R11" t="n">
         <v>11</v>
@@ -7227,10 +7227,10 @@
         <v>182</v>
       </c>
       <c r="P12" t="n">
+        <v>97.252747</v>
+      </c>
+      <c r="Q12" t="n">
         <v>99.450549</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>97.252747</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -7311,10 +7311,10 @@
         <v>1669</v>
       </c>
       <c r="P13" t="n">
+        <v>99.880168</v>
+      </c>
+      <c r="Q13" t="n">
         <v>97.183942</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>99.880168</v>
       </c>
       <c r="R13" t="n">
         <v>93</v>
@@ -8419,10 +8419,10 @@
         <v>944</v>
       </c>
       <c r="P26" t="n">
+        <v>94.385593</v>
+      </c>
+      <c r="Q26" t="n">
         <v>95.65678</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>94.385593</v>
       </c>
       <c r="R26" t="n">
         <v>157</v>
@@ -8503,10 +8503,10 @@
         <v>12</v>
       </c>
       <c r="P27" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q27" t="n">
         <v>91.666667</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>100</v>
       </c>
       <c r="R27" t="n">
         <v>4</v>
@@ -8771,10 +8771,10 @@
         <v>89</v>
       </c>
       <c r="P30" t="n">
+        <v>94.38202200000001</v>
+      </c>
+      <c r="Q30" t="n">
         <v>91.011236</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>94.38202200000001</v>
       </c>
       <c r="R30" t="n">
         <v>21</v>
@@ -8939,10 +8939,10 @@
         <v>16</v>
       </c>
       <c r="P32" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q32" t="n">
         <v>93.75</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>100</v>
       </c>
       <c r="R32" t="n">
         <v>2</v>
@@ -9291,10 +9291,10 @@
         <v>114</v>
       </c>
       <c r="P36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q36" t="n">
         <v>95.614035</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>100</v>
       </c>
       <c r="R36" t="n">
         <v>10</v>
@@ -9627,10 +9627,10 @@
         <v>19</v>
       </c>
       <c r="P40" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q40" t="n">
         <v>89.47368400000001</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>100</v>
       </c>
       <c r="R40" t="n">
         <v>43</v>
@@ -9795,10 +9795,10 @@
         <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -9879,10 +9879,10 @@
         <v>68</v>
       </c>
       <c r="P43" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q43" t="n">
         <v>97.058824</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>100</v>
       </c>
       <c r="R43" t="n">
         <v>19</v>
@@ -10131,10 +10131,10 @@
         <v>1621</v>
       </c>
       <c r="P46" t="n">
+        <v>99.93831</v>
+      </c>
+      <c r="Q46" t="n">
         <v>96.42196199999999</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>99.93831</v>
       </c>
       <c r="R46" t="n">
         <v>51</v>
@@ -11239,10 +11239,10 @@
         <v>943</v>
       </c>
       <c r="P59" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q59" t="n">
         <v>95.227996</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>100</v>
       </c>
       <c r="R59" t="n">
         <v>113</v>
@@ -11323,10 +11323,10 @@
         <v>16</v>
       </c>
       <c r="P60" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q60" t="n">
         <v>93.75</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>100</v>
       </c>
       <c r="R60" t="n">
         <v>11</v>
